--- a/research/traditional_assets/database/data/india/india_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/india/india_insurance_prop_cas.xlsx
@@ -588,49 +588,49 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.167</v>
+        <v>0.171</v>
       </c>
       <c r="E2">
-        <v>0.188</v>
+        <v>0.139</v>
       </c>
       <c r="F2">
-        <v>0.196</v>
+        <v>0.198</v>
       </c>
       <c r="G2">
-        <v>0.08319582768577996</v>
+        <v>0.0384665917285879</v>
       </c>
       <c r="H2">
-        <v>0.08319582768577996</v>
+        <v>0.0384665917285879</v>
       </c>
       <c r="I2">
-        <v>0.05877358690401253</v>
+        <v>0.08352343558712733</v>
       </c>
       <c r="J2">
-        <v>0.04582226254171054</v>
+        <v>0.07430915551970901</v>
       </c>
       <c r="K2">
-        <v>310.4</v>
+        <v>209.6</v>
       </c>
       <c r="L2">
-        <v>0.04573044964346749</v>
+        <v>0.03059809345848966</v>
       </c>
       <c r="M2">
-        <v>0.031</v>
+        <v>58.22770000000001</v>
       </c>
       <c r="N2">
-        <v>2.514396950279828e-06</v>
+        <v>0.005915585537076734</v>
       </c>
       <c r="O2">
-        <v>9.987113402061856e-05</v>
+        <v>0.2778039122137405</v>
       </c>
       <c r="P2">
-        <v>0.031</v>
+        <v>58.22770000000001</v>
       </c>
       <c r="Q2">
-        <v>2.514396950279828e-06</v>
+        <v>0.005915585537076734</v>
       </c>
       <c r="R2">
-        <v>9.987113402061856e-05</v>
+        <v>0.2778039122137405</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,73 +639,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1286</v>
+        <v>1311.2</v>
       </c>
       <c r="V2">
-        <v>0.1043069186470922</v>
+        <v>0.1332100659345125</v>
       </c>
       <c r="W2">
-        <v>0.1050700388613409</v>
+        <v>0.0763368181886757</v>
       </c>
       <c r="X2">
-        <v>0.06604777691186928</v>
+        <v>0.1065555309518772</v>
       </c>
       <c r="Y2">
-        <v>0.03902226194947164</v>
+        <v>-0.0302187127632015</v>
       </c>
       <c r="Z2">
-        <v>1.71395729976866</v>
+        <v>1.197113568314154</v>
       </c>
       <c r="AA2">
-        <v>0.109658337247831</v>
+        <v>0.1103369029699852</v>
       </c>
       <c r="AB2">
-        <v>0.06567750622776675</v>
+        <v>0.1060313613387823</v>
       </c>
       <c r="AC2">
-        <v>0.04398083102006424</v>
+        <v>0.004305541631202919</v>
       </c>
       <c r="AD2">
-        <v>34.4</v>
+        <v>4.3</v>
       </c>
       <c r="AE2">
-        <v>56.84200765162243</v>
+        <v>52.28056942309534</v>
       </c>
       <c r="AF2">
-        <v>91.24200765162243</v>
+        <v>56.58056942309534</v>
       </c>
       <c r="AG2">
-        <v>-1194.757992348378</v>
+        <v>-1254.619430576905</v>
       </c>
       <c r="AH2">
-        <v>0.007346234283954517</v>
+        <v>0.005715393443890946</v>
       </c>
       <c r="AI2">
-        <v>0.01299847018497525</v>
+        <v>0.009166436757970662</v>
       </c>
       <c r="AJ2">
-        <v>-0.1073048341797602</v>
+        <v>-0.1460816520961379</v>
       </c>
       <c r="AK2">
-        <v>-0.2083840720380361</v>
+        <v>-0.2580788343270545</v>
       </c>
       <c r="AL2">
-        <v>6.149999999999999</v>
+        <v>5.000999999999999</v>
       </c>
       <c r="AM2">
-        <v>6.149999999999999</v>
+        <v>5.000999999999999</v>
       </c>
       <c r="AN2">
-        <v>0.08171021377672209</v>
+        <v>0.00728319783197832</v>
       </c>
       <c r="AO2">
-        <v>64.6178861788618</v>
+        <v>113.8172365526895</v>
       </c>
       <c r="AP2">
-        <v>-2.83790496994864</v>
+        <v>-2.125032910868741</v>
       </c>
       <c r="AQ2">
-        <v>64.6178861788618</v>
+        <v>113.8172365526895</v>
       </c>
     </row>
     <row r="3">
@@ -725,121 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.167</v>
+        <v>0.171</v>
       </c>
       <c r="E3">
-        <v>0.188</v>
+        <v>0.139</v>
       </c>
       <c r="F3">
-        <v>0.196</v>
+        <v>0.198</v>
       </c>
       <c r="G3">
-        <v>0.1407255851090374</v>
+        <v>0.1077636152954809</v>
       </c>
       <c r="H3">
-        <v>0.1407255851090374</v>
+        <v>0.1077636152954809</v>
       </c>
       <c r="I3">
-        <v>0.1206647038275363</v>
+        <v>0.1086442641946698</v>
       </c>
       <c r="J3">
-        <v>0.09117466629727203</v>
+        <v>0.08943900143779816</v>
       </c>
       <c r="K3">
-        <v>175.3</v>
+        <v>192.9</v>
       </c>
       <c r="L3">
-        <v>0.08747941514047608</v>
+        <v>0.08940903823870221</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>57.45870000000001</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.007829120736875094</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.2978678071539658</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>57.45870000000001</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.007829120736875094</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.2978678071539658</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="V3">
-        <v>0.00160341484025438</v>
+        <v>0.002043847338229483</v>
       </c>
       <c r="W3">
-        <v>0.1797764331863399</v>
+        <v>0.149708963911525</v>
       </c>
       <c r="X3">
-        <v>0.06578912918986751</v>
+        <v>0.1060778842266774</v>
       </c>
       <c r="Y3">
-        <v>0.1139873039964724</v>
+        <v>0.04363107968484767</v>
       </c>
       <c r="Z3">
-        <v>1.931562966889971</v>
+        <v>1.649338735570675</v>
       </c>
       <c r="AA3">
-        <v>0.1761096089383618</v>
+        <v>0.1475152095421218</v>
       </c>
       <c r="AB3">
-        <v>0.06565421292168964</v>
+        <v>0.1060461799663867</v>
       </c>
       <c r="AC3">
-        <v>0.1104553960166722</v>
+        <v>0.04146902957573514</v>
       </c>
       <c r="AD3">
-        <v>34.4</v>
+        <v>4.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>34.4</v>
+        <v>4.3</v>
       </c>
       <c r="AG3">
-        <v>19.6</v>
+        <v>-10.7</v>
       </c>
       <c r="AH3">
-        <v>0.003713018230487766</v>
+        <v>0.0005855598224255794</v>
       </c>
       <c r="AI3">
-        <v>0.02600347720916169</v>
+        <v>0.003374931324071894</v>
       </c>
       <c r="AJ3">
-        <v>0.002118941826398123</v>
+        <v>-0.001460073140112439</v>
       </c>
       <c r="AK3">
-        <v>0.01498356394771042</v>
+        <v>-0.008498133587483123</v>
       </c>
       <c r="AL3">
-        <v>5.39</v>
+        <v>4.47</v>
       </c>
       <c r="AM3">
-        <v>5.39</v>
+        <v>4.47</v>
       </c>
       <c r="AN3">
-        <v>0.140983606557377</v>
+        <v>0.01832907075873828</v>
       </c>
       <c r="AO3">
-        <v>44.86085343228201</v>
+        <v>52.43847874720358</v>
       </c>
       <c r="AP3">
-        <v>0.080327868852459</v>
+        <v>-0.04560954816709292</v>
       </c>
       <c r="AQ3">
-        <v>44.86085343228201</v>
+        <v>52.43847874720358</v>
       </c>
     </row>
     <row r="4">
@@ -850,7 +853,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The New India Assurance Company Limited (BSE:540769)</t>
+          <t>The New India Assurance Company Limited (NSEI:NIACL)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,40 +862,40 @@
         </is>
       </c>
       <c r="G4">
-        <v>0.05909651524970212</v>
+        <v>0.006606145846652175</v>
       </c>
       <c r="H4">
-        <v>0.05909651524970212</v>
+        <v>0.006606145846652175</v>
       </c>
       <c r="I4">
-        <v>0.03284729361575256</v>
+        <v>0.07197372162881577</v>
       </c>
       <c r="J4">
-        <v>0.02639862565204313</v>
+        <v>0.06881642135404893</v>
       </c>
       <c r="K4">
-        <v>135.1</v>
+        <v>16.7</v>
       </c>
       <c r="L4">
-        <v>0.02824173756715513</v>
+        <v>0.003558794698035204</v>
       </c>
       <c r="M4">
-        <v>0.031</v>
+        <v>0.769</v>
       </c>
       <c r="N4">
-        <v>1.000419530770968e-05</v>
+        <v>0.0003071086261980831</v>
       </c>
       <c r="O4">
-        <v>0.000229459659511473</v>
+        <v>0.04604790419161677</v>
       </c>
       <c r="P4">
-        <v>0.031</v>
+        <v>0.769</v>
       </c>
       <c r="Q4">
-        <v>1.000419530770968e-05</v>
+        <v>0.0003071086261980831</v>
       </c>
       <c r="R4">
-        <v>0.000229459659511473</v>
+        <v>0.04604790419161677</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -901,73 +904,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1271.2</v>
+        <v>1296.2</v>
       </c>
       <c r="V4">
-        <v>0.4102365508116307</v>
+        <v>0.5176517571884984</v>
       </c>
       <c r="W4">
-        <v>0.03036364453634198</v>
+        <v>0.00296467246582638</v>
       </c>
       <c r="X4">
-        <v>0.06630642463387104</v>
+        <v>0.107033177677077</v>
       </c>
       <c r="Y4">
-        <v>-0.03594278009752906</v>
+        <v>-0.1040685052112506</v>
       </c>
       <c r="Z4">
-        <v>1.636716476335053</v>
+        <v>1.063097948983135</v>
       </c>
       <c r="AA4">
-        <v>0.04320706555730016</v>
+        <v>0.07315859639784862</v>
       </c>
       <c r="AB4">
-        <v>0.06570079953384383</v>
+        <v>0.1060165427111779</v>
       </c>
       <c r="AC4">
-        <v>-0.02249373397654367</v>
+        <v>-0.03285794631332931</v>
       </c>
       <c r="AD4">
         <v>0</v>
       </c>
       <c r="AE4">
-        <v>56.84200765162243</v>
+        <v>52.28056942309534</v>
       </c>
       <c r="AF4">
-        <v>56.84200765162243</v>
+        <v>52.28056942309534</v>
       </c>
       <c r="AG4">
-        <v>-1214.357992348378</v>
+        <v>-1243.919430576905</v>
       </c>
       <c r="AH4">
-        <v>0.01801338962174827</v>
+        <v>0.02045181192097943</v>
       </c>
       <c r="AI4">
-        <v>0.00997833555431909</v>
+        <v>0.01067281347392433</v>
       </c>
       <c r="AJ4">
-        <v>-0.6444467020409856</v>
+        <v>-0.9871745194407769</v>
       </c>
       <c r="AK4">
-        <v>-0.274409975601591</v>
+        <v>-0.3453144214072471</v>
       </c>
       <c r="AL4">
-        <v>0.76</v>
+        <v>0.531</v>
       </c>
       <c r="AM4">
-        <v>0.76</v>
+        <v>0.531</v>
       </c>
       <c r="AN4">
         <v>0</v>
       </c>
       <c r="AO4">
-        <v>204.7368421052632</v>
+        <v>630.5084745762712</v>
       </c>
       <c r="AP4">
-        <v>-6.860779617787444</v>
+        <v>-3.49611981612396</v>
       </c>
       <c r="AQ4">
-        <v>204.7368421052632</v>
+        <v>630.5084745762712</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/india/india_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/india/india_insurance_prop_cas.xlsx
@@ -588,49 +588,49 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.171</v>
+        <v>0.166</v>
       </c>
       <c r="E2">
-        <v>0.139</v>
+        <v>0.114</v>
       </c>
       <c r="F2">
-        <v>0.198</v>
+        <v>0.17</v>
       </c>
       <c r="G2">
-        <v>0.0384665917285879</v>
+        <v>0.1147923218739833</v>
       </c>
       <c r="H2">
-        <v>0.0384665917285879</v>
+        <v>0.1147923218739833</v>
       </c>
       <c r="I2">
-        <v>0.08352343558712733</v>
+        <v>0.07163686716373643</v>
       </c>
       <c r="J2">
-        <v>0.07430915551970901</v>
+        <v>0.05735222122101032</v>
       </c>
       <c r="K2">
-        <v>209.6</v>
+        <v>325.5</v>
       </c>
       <c r="L2">
-        <v>0.03059809345848966</v>
+        <v>0.04412482377182518</v>
       </c>
       <c r="M2">
-        <v>58.22770000000001</v>
+        <v>108.5416</v>
       </c>
       <c r="N2">
-        <v>0.005915585537076734</v>
+        <v>0.008495276558109683</v>
       </c>
       <c r="O2">
-        <v>0.2778039122137405</v>
+        <v>0.3334611367127496</v>
       </c>
       <c r="P2">
-        <v>58.22770000000001</v>
+        <v>108.5416</v>
       </c>
       <c r="Q2">
-        <v>0.005915585537076734</v>
+        <v>0.008495276558109683</v>
       </c>
       <c r="R2">
-        <v>0.2778039122137405</v>
+        <v>0.3334611367127496</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,73 +639,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1311.2</v>
+        <v>1373.86</v>
       </c>
       <c r="V2">
-        <v>0.1332100659345125</v>
+        <v>0.1075285480601407</v>
       </c>
       <c r="W2">
-        <v>0.0763368181886757</v>
+        <v>0.09506012486943334</v>
       </c>
       <c r="X2">
-        <v>0.1065555309518772</v>
+        <v>0.09061933600206912</v>
       </c>
       <c r="Y2">
-        <v>-0.0302187127632015</v>
+        <v>0.004440788867364223</v>
       </c>
       <c r="Z2">
-        <v>1.197113568314154</v>
+        <v>1.520473735505225</v>
       </c>
       <c r="AA2">
-        <v>0.1103369029699852</v>
+        <v>0.1138734050738601</v>
       </c>
       <c r="AB2">
-        <v>0.1060313613387823</v>
+        <v>0.09038838547479687</v>
       </c>
       <c r="AC2">
-        <v>0.004305541631202919</v>
+        <v>0.02348501959906323</v>
       </c>
       <c r="AD2">
-        <v>4.3</v>
+        <v>4.21</v>
       </c>
       <c r="AE2">
-        <v>52.28056942309534</v>
+        <v>49.74579153274586</v>
       </c>
       <c r="AF2">
-        <v>56.58056942309534</v>
+        <v>53.95579153274586</v>
       </c>
       <c r="AG2">
-        <v>-1254.619430576905</v>
+        <v>-1319.904208467254</v>
       </c>
       <c r="AH2">
-        <v>0.005715393443890946</v>
+        <v>0.004205224768663232</v>
       </c>
       <c r="AI2">
-        <v>0.009166436757970662</v>
+        <v>0.008129476868580824</v>
       </c>
       <c r="AJ2">
-        <v>-0.1460816520961379</v>
+        <v>-0.1152070991299978</v>
       </c>
       <c r="AK2">
-        <v>-0.2580788343270545</v>
+        <v>-0.2507799938947117</v>
       </c>
       <c r="AL2">
-        <v>5.000999999999999</v>
+        <v>1.531</v>
       </c>
       <c r="AM2">
-        <v>5.000999999999999</v>
+        <v>1.531</v>
       </c>
       <c r="AN2">
-        <v>0.00728319783197832</v>
+        <v>0.007693713450292397</v>
       </c>
       <c r="AO2">
-        <v>113.8172365526895</v>
+        <v>343.958197256695</v>
       </c>
       <c r="AP2">
-        <v>-2.125032910868741</v>
+        <v>-2.412105644128754</v>
       </c>
       <c r="AQ2">
-        <v>113.8172365526895</v>
+        <v>343.958197256695</v>
       </c>
     </row>
     <row r="3">
@@ -725,49 +725,49 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.171</v>
+        <v>0.166</v>
       </c>
       <c r="E3">
-        <v>0.139</v>
+        <v>0.114</v>
       </c>
       <c r="F3">
-        <v>0.198</v>
+        <v>0.151</v>
       </c>
       <c r="G3">
-        <v>0.1077636152954809</v>
+        <v>0.1093976702731833</v>
       </c>
       <c r="H3">
-        <v>0.1077636152954809</v>
+        <v>0.1093976702731833</v>
       </c>
       <c r="I3">
-        <v>0.1086442641946698</v>
+        <v>0.1172325166853211</v>
       </c>
       <c r="J3">
-        <v>0.08943900143779816</v>
+        <v>0.08874258152807947</v>
       </c>
       <c r="K3">
-        <v>192.9</v>
+        <v>211.5</v>
       </c>
       <c r="L3">
-        <v>0.08940903823870221</v>
+        <v>0.08767566223106578</v>
       </c>
       <c r="M3">
-        <v>57.45870000000001</v>
+        <v>61.9416</v>
       </c>
       <c r="N3">
-        <v>0.007829120736875094</v>
+        <v>0.00729737753587333</v>
       </c>
       <c r="O3">
-        <v>0.2978678071539658</v>
+        <v>0.292868085106383</v>
       </c>
       <c r="P3">
-        <v>57.45870000000001</v>
+        <v>61.9416</v>
       </c>
       <c r="Q3">
-        <v>0.007829120736875094</v>
+        <v>0.00729737753587333</v>
       </c>
       <c r="R3">
-        <v>0.2978678071539658</v>
+        <v>0.292868085106383</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -776,73 +776,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>15</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="V3">
-        <v>0.002043847338229483</v>
+        <v>0.0009966777408637875</v>
       </c>
       <c r="W3">
-        <v>0.149708963911525</v>
+        <v>0.1665616632540558</v>
       </c>
       <c r="X3">
-        <v>0.1060778842266774</v>
+        <v>0.09041879742491921</v>
       </c>
       <c r="Y3">
-        <v>0.04363107968484767</v>
+        <v>0.07614286582913657</v>
       </c>
       <c r="Z3">
-        <v>1.649338735570675</v>
+        <v>1.915892304026686</v>
       </c>
       <c r="AA3">
-        <v>0.1475152095421218</v>
+        <v>0.1700212289891082</v>
       </c>
       <c r="AB3">
-        <v>0.1060461799663867</v>
+        <v>0.09039791319944052</v>
       </c>
       <c r="AC3">
-        <v>0.04146902957573514</v>
+        <v>0.07962331578966766</v>
       </c>
       <c r="AD3">
-        <v>4.3</v>
+        <v>4.21</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4.3</v>
+        <v>4.21</v>
       </c>
       <c r="AG3">
-        <v>-10.7</v>
+        <v>-4.250000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.0005855598224255794</v>
+        <v>0.0004957367814318903</v>
       </c>
       <c r="AI3">
-        <v>0.003374931324071894</v>
+        <v>0.002927453393690329</v>
       </c>
       <c r="AJ3">
-        <v>-0.001460073140112439</v>
+        <v>-0.0005009459037358778</v>
       </c>
       <c r="AK3">
-        <v>-0.008498133587483123</v>
+        <v>-0.002972755569544994</v>
       </c>
       <c r="AL3">
-        <v>4.47</v>
+        <v>1.38</v>
       </c>
       <c r="AM3">
-        <v>4.47</v>
+        <v>1.38</v>
       </c>
       <c r="AN3">
-        <v>0.01832907075873828</v>
+        <v>0.01490265486725664</v>
       </c>
       <c r="AO3">
-        <v>52.43847874720358</v>
+        <v>204.9275362318841</v>
       </c>
       <c r="AP3">
-        <v>-0.04560954816709292</v>
+        <v>-0.01504424778761062</v>
       </c>
       <c r="AQ3">
-        <v>52.43847874720358</v>
+        <v>204.9275362318841</v>
       </c>
     </row>
     <row r="4">
@@ -861,41 +861,44 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="F4">
+        <v>0.189</v>
+      </c>
       <c r="G4">
-        <v>0.006606145846652175</v>
+        <v>0.1174136368214322</v>
       </c>
       <c r="H4">
-        <v>0.006606145846652175</v>
+        <v>0.1174136368214322</v>
       </c>
       <c r="I4">
-        <v>0.07197372162881577</v>
+        <v>0.04948148689564928</v>
       </c>
       <c r="J4">
-        <v>0.06881642135404893</v>
+        <v>0.04177294665226178</v>
       </c>
       <c r="K4">
-        <v>16.7</v>
+        <v>114</v>
       </c>
       <c r="L4">
-        <v>0.003558794698035204</v>
+        <v>0.02296303756672374</v>
       </c>
       <c r="M4">
-        <v>0.769</v>
+        <v>46.6</v>
       </c>
       <c r="N4">
-        <v>0.0003071086261980831</v>
+        <v>0.01086627025766585</v>
       </c>
       <c r="O4">
-        <v>0.04604790419161677</v>
+        <v>0.4087719298245614</v>
       </c>
       <c r="P4">
-        <v>0.769</v>
+        <v>46.6</v>
       </c>
       <c r="Q4">
-        <v>0.0003071086261980831</v>
+        <v>0.01086627025766585</v>
       </c>
       <c r="R4">
-        <v>0.04604790419161677</v>
+        <v>0.4087719298245614</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -904,73 +907,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1296.2</v>
+        <v>1365.4</v>
       </c>
       <c r="V4">
-        <v>0.5176517571884984</v>
+        <v>0.3183863821849132</v>
       </c>
       <c r="W4">
-        <v>0.00296467246582638</v>
+        <v>0.02355858648481091</v>
       </c>
       <c r="X4">
-        <v>0.107033177677077</v>
+        <v>0.09081987457921903</v>
       </c>
       <c r="Y4">
-        <v>-0.1040685052112506</v>
+        <v>-0.06726128809440812</v>
       </c>
       <c r="Z4">
-        <v>1.063097948983135</v>
+        <v>1.381889136027384</v>
       </c>
       <c r="AA4">
-        <v>0.07315859639784862</v>
+        <v>0.05772558115861202</v>
       </c>
       <c r="AB4">
-        <v>0.1060165427111779</v>
+        <v>0.09037885775015322</v>
       </c>
       <c r="AC4">
-        <v>-0.03285794631332931</v>
+        <v>-0.0326532765915412</v>
       </c>
       <c r="AD4">
         <v>0</v>
       </c>
       <c r="AE4">
-        <v>52.28056942309534</v>
+        <v>49.74579153274586</v>
       </c>
       <c r="AF4">
-        <v>52.28056942309534</v>
+        <v>49.74579153274586</v>
       </c>
       <c r="AG4">
-        <v>-1243.919430576905</v>
+        <v>-1315.654208467254</v>
       </c>
       <c r="AH4">
-        <v>0.02045181192097943</v>
+        <v>0.01146679877609474</v>
       </c>
       <c r="AI4">
-        <v>0.01067281347392433</v>
+        <v>0.00956843820409981</v>
       </c>
       <c r="AJ4">
-        <v>-0.9871745194407769</v>
+        <v>-0.4425571660038668</v>
       </c>
       <c r="AK4">
-        <v>-0.3453144214072471</v>
+        <v>-0.3431951201347783</v>
       </c>
       <c r="AL4">
-        <v>0.531</v>
+        <v>0.151</v>
       </c>
       <c r="AM4">
-        <v>0.531</v>
+        <v>0.151</v>
       </c>
       <c r="AN4">
         <v>0</v>
       </c>
       <c r="AO4">
-        <v>630.5084745762712</v>
+        <v>1614.569536423841</v>
       </c>
       <c r="AP4">
-        <v>-3.49611981612396</v>
+        <v>-4.970359684424837</v>
       </c>
       <c r="AQ4">
-        <v>630.5084745762712</v>
+        <v>1614.569536423841</v>
       </c>
     </row>
   </sheetData>
